--- a/Conversion Script/Set_filter_file_Europe2060.xlsx
+++ b/Conversion Script/Set_filter_file_Europe2060.xlsx
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B156"/>
+  <dimension ref="A1:B157"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2580,6 +2580,16 @@
         </is>
       </c>
       <c r="B156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>HD_Gas_Boiler</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
         <v>0</v>
       </c>
     </row>
